--- a/SubRES_Tmpl/SubRES_New_RE_Trans.xlsx
+++ b/SubRES_Tmpl/SubRES_New_RE_Trans.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VS_CEA_8C\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{78C7E4CF-D0D8-44AE-A048-7F430F876E0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F797C392-C611-4673-A8D6-A07726BDA229}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2573" yWindow="2573" windowWidth="21600" windowHeight="12772" xr2:uid="{8AEC0A57-CA8D-4DED-8178-B4715A777C65}"/>
+    <workbookView xWindow="368" yWindow="368" windowWidth="21599" windowHeight="12772" xr2:uid="{5FF52315-3698-4C02-A5F9-3CBC2BCF3920}"/>
   </bookViews>
   <sheets>
     <sheet name="AVA_common" sheetId="3" r:id="rId1"/>
@@ -264,46 +264,46 @@
     <t>FRA</t>
   </si>
   <si>
+    <t>*[_]GBR*</t>
+  </si>
+  <si>
+    <t>GBR</t>
+  </si>
+  <si>
     <t>*[_]BEL*</t>
   </si>
   <si>
     <t>BEL</t>
   </si>
   <si>
-    <t>*[_]GBR*</t>
-  </si>
-  <si>
-    <t>GBR</t>
+    <t>*[_]DEU*</t>
+  </si>
+  <si>
+    <t>DEU</t>
+  </si>
+  <si>
+    <t>*[_]CHE*</t>
+  </si>
+  <si>
+    <t>CHE</t>
+  </si>
+  <si>
+    <t>*[_]ITA*</t>
+  </si>
+  <si>
+    <t>ITA</t>
+  </si>
+  <si>
+    <t>*[_]ESP*</t>
+  </si>
+  <si>
+    <t>ESP</t>
   </si>
   <si>
     <t>*[_]NLD*</t>
   </si>
   <si>
     <t>NLD</t>
-  </si>
-  <si>
-    <t>*[_]DEU*</t>
-  </si>
-  <si>
-    <t>DEU</t>
-  </si>
-  <si>
-    <t>*[_]CHE*</t>
-  </si>
-  <si>
-    <t>CHE</t>
-  </si>
-  <si>
-    <t>*[_]ITA*</t>
-  </si>
-  <si>
-    <t>ITA</t>
-  </si>
-  <si>
-    <t>*[_]ESP*</t>
-  </si>
-  <si>
-    <t>ESP</t>
   </si>
 </sst>
 </file>
@@ -664,7 +664,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D495304-43C8-4A6F-9403-5EBA758995B4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA9F0D1B-9064-42D1-A7F5-92507E7EE5FE}">
   <dimension ref="B2:C11"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -751,7 +751,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAE4372D-F630-485B-A3C1-A68703A064D5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAE5E23E-EE55-4973-A19B-A939D760D724}">
   <dimension ref="C4:X58"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>

--- a/SubRES_Tmpl/SubRES_New_RE_Trans.xlsx
+++ b/SubRES_Tmpl/SubRES_New_RE_Trans.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VS_CEA_8C\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F797C392-C611-4673-A8D6-A07726BDA229}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CB77A0C5-A1D6-4DDD-BA65-B7037EC2E543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="368" yWindow="368" windowWidth="21599" windowHeight="12772" xr2:uid="{5FF52315-3698-4C02-A5F9-3CBC2BCF3920}"/>
+    <workbookView xWindow="4043" yWindow="4043" windowWidth="21599" windowHeight="12772" xr2:uid="{38D10395-3790-4AEB-B072-A51D0BD9DB19}"/>
   </bookViews>
   <sheets>
     <sheet name="AVA_common" sheetId="3" r:id="rId1"/>
@@ -664,7 +664,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA9F0D1B-9064-42D1-A7F5-92507E7EE5FE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCC2F9D5-E0B2-4A51-B398-0266CA6B8537}">
   <dimension ref="B2:C11"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -751,7 +751,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAE5E23E-EE55-4973-A19B-A939D760D724}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5EC034E2-E610-4C72-AB2F-7FBC8EB2464C}">
   <dimension ref="C4:X58"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>

--- a/SubRES_Tmpl/SubRES_New_RE_Trans.xlsx
+++ b/SubRES_Tmpl/SubRES_New_RE_Trans.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VS_CEA_8C\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CB77A0C5-A1D6-4DDD-BA65-B7037EC2E543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D209F866-9F6C-4998-BA6E-7BA81C58F859}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4043" yWindow="4043" windowWidth="21599" windowHeight="12772" xr2:uid="{38D10395-3790-4AEB-B072-A51D0BD9DB19}"/>
+    <workbookView xWindow="4043" yWindow="4043" windowWidth="21599" windowHeight="12772" xr2:uid="{A76C262D-6FDB-4A7D-AA57-BA682D102F4B}"/>
   </bookViews>
   <sheets>
     <sheet name="AVA_common" sheetId="3" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="98">
   <si>
     <t>~TFM_INS</t>
   </si>
@@ -177,12 +177,42 @@
     <t>io</t>
   </si>
   <si>
+    <t>other_indexes</t>
+  </si>
+  <si>
+    <t>pset_set</t>
+  </si>
+  <si>
+    <t>allregions</t>
+  </si>
+  <si>
+    <t>top_check</t>
+  </si>
+  <si>
     <t>ELC_spv*</t>
   </si>
   <si>
     <t>IN</t>
   </si>
   <si>
+    <t>FLO_FUNC</t>
+  </si>
+  <si>
+    <t>AuxStoOUT</t>
+  </si>
+  <si>
+    <t>STG</t>
+  </si>
+  <si>
+    <t>en[_]*?h*</t>
+  </si>
+  <si>
+    <t>ELC,e[_]*</t>
+  </si>
+  <si>
+    <t>OUT</t>
+  </si>
+  <si>
     <t>ELC_wo*</t>
   </si>
   <si>
@@ -192,6 +222,9 @@
     <t>windoff</t>
   </si>
   <si>
+    <t>~TFM_TOPINS-A</t>
+  </si>
+  <si>
     <t>windon</t>
   </si>
   <si>
@@ -225,15 +258,9 @@
     <t>en_biomass_cofiring*,en_geothermal*</t>
   </si>
   <si>
-    <t>pset_set</t>
-  </si>
-  <si>
     <t>limtype</t>
   </si>
   <si>
-    <t>other_indexes</t>
-  </si>
-  <si>
     <t>flo_emis</t>
   </si>
   <si>
@@ -270,6 +297,12 @@
     <t>GBR</t>
   </si>
   <si>
+    <t>*[_]NLD*</t>
+  </si>
+  <si>
+    <t>NLD</t>
+  </si>
+  <si>
     <t>*[_]BEL*</t>
   </si>
   <si>
@@ -298,22 +331,32 @@
   </si>
   <si>
     <t>ESP</t>
-  </si>
-  <si>
-    <t>*[_]NLD*</t>
-  </si>
-  <si>
-    <t>NLD</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -334,7 +377,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -342,17 +385,42 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="2"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFill="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="3">
+    <cellStyle name="Heading 2" xfId="1" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="2" builtinId="18"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -664,13 +732,13 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCC2F9D5-E0B2-4A51-B398-0266CA6B8537}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44B06566-903A-4F2D-BCCD-75CCE62A0BDC}">
   <dimension ref="B2:C11"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="2" spans="2:3" x14ac:dyDescent="0.45">
       <c r="B2" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.45">
@@ -678,71 +746,71 @@
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.45">
       <c r="B4" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="C4" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.45">
       <c r="B5" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="C5" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.45">
       <c r="B6" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="C6" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.45">
       <c r="B7" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="C7" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.45">
       <c r="B8" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="C8" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.45">
       <c r="B9" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="C9" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.45">
       <c r="B10" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="C10" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="C11" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -751,7 +819,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5EC034E2-E610-4C72-AB2F-7FBC8EB2464C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{690B9BC6-39BD-4764-8955-B2CB0BE88A57}">
   <dimension ref="C4:X58"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
@@ -765,6 +833,13 @@
     <col min="11" max="11" width="5" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="6.265625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="4.265625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.86328125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.3984375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.59765625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.73046875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="9.06640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="4" spans="3:24" x14ac:dyDescent="0.45">
@@ -1387,7 +1462,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="33" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="33" spans="3:22" x14ac:dyDescent="0.45">
       <c r="D33" t="s">
         <v>20</v>
       </c>
@@ -1398,7 +1473,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="34" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="34" spans="3:22" x14ac:dyDescent="0.45">
       <c r="D34" t="s">
         <v>18</v>
       </c>
@@ -1409,7 +1484,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="35" spans="3:22" x14ac:dyDescent="0.45">
       <c r="C35" t="s">
         <v>40</v>
       </c>
@@ -1423,7 +1498,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="36" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="36" spans="3:22" x14ac:dyDescent="0.45">
       <c r="C36" t="s">
         <v>38</v>
       </c>
@@ -1434,12 +1509,15 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="39" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="39" spans="3:22" ht="17.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="C39" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="40" spans="3:7" x14ac:dyDescent="0.45">
+      <c r="P39" s="4" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="3:22" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="C40" t="s">
         <v>3</v>
       </c>
@@ -1449,63 +1527,134 @@
       <c r="E40" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="41" spans="3:7" x14ac:dyDescent="0.45">
+      <c r="P40" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q40" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="R40" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="S40" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="T40" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="U40" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="V40" s="6" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="41" spans="3:22" x14ac:dyDescent="0.45">
       <c r="C41" t="s">
         <v>19</v>
       </c>
       <c r="D41" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="E41" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="42" spans="3:7" x14ac:dyDescent="0.45">
+        <v>51</v>
+      </c>
+      <c r="P41" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>53</v>
+      </c>
+      <c r="R41" t="s">
+        <v>54</v>
+      </c>
+      <c r="S41">
+        <v>1</v>
+      </c>
+      <c r="T41" t="s">
+        <v>55</v>
+      </c>
+      <c r="U41" t="s">
+        <v>56</v>
+      </c>
+      <c r="V41" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="42" spans="3:22" x14ac:dyDescent="0.45">
       <c r="C42" t="s">
         <v>34</v>
       </c>
       <c r="D42" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="E42" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="43" spans="3:7" x14ac:dyDescent="0.45">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="43" spans="3:22" x14ac:dyDescent="0.45">
       <c r="C43" t="s">
         <v>13</v>
       </c>
       <c r="D43" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="E43" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="44" spans="3:7" x14ac:dyDescent="0.45">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="44" spans="3:22" ht="17.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="C44" t="s">
         <v>30</v>
       </c>
       <c r="D44" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="E44" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="45" spans="3:7" x14ac:dyDescent="0.45">
+        <v>51</v>
+      </c>
+      <c r="P44" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="45" spans="3:22" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="C45" t="s">
         <v>32</v>
       </c>
       <c r="D45" t="s">
+        <v>62</v>
+      </c>
+      <c r="E45" t="s">
         <v>51</v>
       </c>
-      <c r="E45" t="s">
+      <c r="P45" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q45" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="R45" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="S45" s="6" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="48" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="46" spans="3:22" x14ac:dyDescent="0.45">
+      <c r="P46" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q46" t="s">
+        <v>53</v>
+      </c>
+      <c r="R46" t="s">
+        <v>57</v>
+      </c>
+      <c r="S46" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="48" spans="3:22" x14ac:dyDescent="0.45">
       <c r="C48" t="s">
         <v>0</v>
       </c>
@@ -1521,52 +1670,52 @@
         <v>36</v>
       </c>
       <c r="F49" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="G49" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
     </row>
     <row r="50" spans="3:13" x14ac:dyDescent="0.45">
       <c r="C50" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="D50">
         <v>2025</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="G50" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
     </row>
     <row r="51" spans="3:13" x14ac:dyDescent="0.45">
       <c r="C51" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="D51">
         <v>40</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="G51" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
     </row>
     <row r="52" spans="3:13" x14ac:dyDescent="0.45">
       <c r="C52" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="D52">
         <v>2100</v>
       </c>
       <c r="F52" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
     </row>
     <row r="55" spans="3:13" x14ac:dyDescent="0.45">
@@ -1579,10 +1728,10 @@
         <v>1</v>
       </c>
       <c r="D56" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="E56" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="F56" t="s">
         <v>3</v>
@@ -1600,10 +1749,10 @@
         <v>2030</v>
       </c>
       <c r="K56" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="L56" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="M56" t="s">
         <v>44</v>
@@ -1611,42 +1760,42 @@
     </row>
     <row r="57" spans="3:13" x14ac:dyDescent="0.45">
       <c r="C57" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="E57" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="F57" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="I57">
         <v>0.95</v>
       </c>
       <c r="L57" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="M57" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
     </row>
     <row r="58" spans="3:13" x14ac:dyDescent="0.45">
       <c r="C58" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="E58" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="F58" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="I58">
         <v>0.85</v>
       </c>
       <c r="L58" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="M58" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
